--- a/output/laminas_comunales/comunal_s_isapre_a_2021_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2021_los_lagos.xlsx
@@ -375,91 +375,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Puerto Varas</t>
         </is>
       </c>
       <c r="C2">
-        <v>38609</v>
+        <v>27.48216380454222</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="C3">
-        <v>22468</v>
+        <v>14.68704113695326</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="C4">
-        <v>14291</v>
+        <v>14.60368850089611</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="C5">
-        <v>7578</v>
+        <v>13.11173099592666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="C6">
-        <v>3165</v>
+        <v>10.07974827754571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Curaco de Vélez</t>
         </is>
       </c>
       <c r="C7">
-        <v>2068</v>
+        <v>9.931686810299528</v>
       </c>
     </row>
     <row r="8">
@@ -474,292 +474,292 @@
         </is>
       </c>
       <c r="C8">
-        <v>2034</v>
+        <v>9.923403424891447</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>Chonchi</t>
         </is>
       </c>
       <c r="C9">
-        <v>1858</v>
+        <v>9.458606764260475</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chonchi</t>
+          <t>Quinchao</t>
         </is>
       </c>
       <c r="C10">
-        <v>1499</v>
+        <v>7.775723967960567</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>Ancud</t>
         </is>
       </c>
       <c r="C11">
-        <v>1493</v>
+        <v>7.144953382847597</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Quellón</t>
         </is>
       </c>
       <c r="C12">
-        <v>1058</v>
+        <v>6.976587274812766</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Dalcahue</t>
         </is>
       </c>
       <c r="C13">
-        <v>1012</v>
+        <v>6.861219195849546</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>Puqueldón</t>
         </is>
       </c>
       <c r="C14">
-        <v>708</v>
+        <v>6.209905055170644</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
+          <t>Puerto Octay</t>
         </is>
       </c>
       <c r="C15">
-        <v>648</v>
+        <v>5.483503981797497</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Quinchao</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="C16">
-        <v>631</v>
+        <v>5.066237021124239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Purranque</t>
         </is>
       </c>
       <c r="C17">
-        <v>526</v>
+        <v>4.920264488525866</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Puyehue</t>
+          <t>Río Negro</t>
         </is>
       </c>
       <c r="C18">
-        <v>515</v>
+        <v>4.743718592964824</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Maullín</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="C19">
-        <v>491</v>
+        <v>4.714106470693673</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
+          <t>Quemchi</t>
         </is>
       </c>
       <c r="C20">
-        <v>482</v>
+        <v>4.391033048301363</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fresia</t>
+          <t>Puyehue</t>
         </is>
       </c>
       <c r="C21">
-        <v>462</v>
+        <v>4.31974500922664</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quemchi</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="C22">
-        <v>380</v>
+        <v>4.129328465538223</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>Chaitén</t>
         </is>
       </c>
       <c r="C23">
-        <v>378</v>
+        <v>3.880070546737213</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
+          <t>Fresia</t>
         </is>
       </c>
       <c r="C24">
-        <v>354</v>
+        <v>3.734238603297769</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Hualaihué</t>
         </is>
       </c>
       <c r="C25">
-        <v>283</v>
+        <v>3.725531467059566</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
+          <t>Los Muermos</t>
         </is>
       </c>
       <c r="C26">
-        <v>242</v>
+        <v>3.65647218146936</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chaitén</t>
+          <t>Palena</t>
         </is>
       </c>
       <c r="C27">
-        <v>176</v>
+        <v>3.654320987654321</v>
       </c>
     </row>
     <row r="28">
@@ -774,22 +774,22 @@
         </is>
       </c>
       <c r="C28">
-        <v>148</v>
+        <v>3.591361320067945</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>San Juan de la Costa</t>
+          <t>Maullín</t>
         </is>
       </c>
       <c r="C29">
-        <v>141</v>
+        <v>3.208311552535285</v>
       </c>
     </row>
     <row r="30">
@@ -804,22 +804,22 @@
         </is>
       </c>
       <c r="C30">
-        <v>83</v>
+        <v>3.070662227155013</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Palena</t>
+          <t>San Juan de la Costa</t>
         </is>
       </c>
       <c r="C31">
-        <v>74</v>
+        <v>1.737309019221291</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +875,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
